--- a/data/trans_orig/P36BPD07_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023</t>
+          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118755</t>
+          <t>118050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>157117</t>
+          <t>156842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148212</t>
+          <t>148178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183109</t>
+          <t>183288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>273954</t>
+          <t>275586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>326721</t>
+          <t>326855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355766</t>
+          <t>356041</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394128</t>
+          <t>394833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>572399</t>
+          <t>572220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>607296</t>
+          <t>607330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>941670</t>
+          <t>941536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>994437</t>
+          <t>992805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,27%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>450838</t>
+          <t>425723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>729730</t>
+          <t>731284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>376902</t>
+          <t>368131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>570434</t>
+          <t>577074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>933204</t>
+          <t>912437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1276310</t>
+          <t>1273737</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1557811</t>
+          <t>1556257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1836703</t>
+          <t>1861818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1663117</t>
+          <t>1656477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1856649</t>
+          <t>1865420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3244782</t>
+          <t>3247355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3587888</t>
+          <t>3608655</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,82%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106170</t>
+          <t>106761</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156167</t>
+          <t>157867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88901</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122240</t>
+          <t>121821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205627</t>
+          <t>203100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264293</t>
+          <t>267145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>490456</t>
+          <t>488756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540453</t>
+          <t>539862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537016</t>
+          <t>537435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>570355</t>
+          <t>571207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1041586</t>
+          <t>1038734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1100252</t>
+          <t>1102779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>699415</t>
+          <t>682918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>990758</t>
+          <t>990645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>629483</t>
+          <t>635958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>838176</t>
+          <t>841275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1455005</t>
+          <t>1429680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1800967</t>
+          <t>1803121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2456289</t>
+          <t>2456402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2747632</t>
+          <t>2764129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2810139</t>
+          <t>2807040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3018832</t>
+          <t>3012357</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5294395</t>
+          <t>5292241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5640357</t>
+          <t>5665682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD07_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>137545</t>
+          <t>148046</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118050</t>
+          <t>128106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156842</t>
+          <t>168480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>164800</t>
+          <t>186401</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148178</t>
+          <t>167329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183288</t>
+          <t>208386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>302345</t>
+          <t>334446</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>275586</t>
+          <t>305743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>326855</t>
+          <t>365366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>375338</t>
+          <t>428348</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356041</t>
+          <t>407914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394833</t>
+          <t>448288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>590708</t>
+          <t>635637</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>572220</t>
+          <t>613652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>607330</t>
+          <t>654709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>966046</t>
+          <t>1063986</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>941536</t>
+          <t>1033066</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>992805</t>
+          <t>1092689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512883</t>
+          <t>576394</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512883</t>
+          <t>576394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512883</t>
+          <t>576394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268391</t>
+          <t>1398432</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268391</t>
+          <t>1398432</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268391</t>
+          <t>1398432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>636316</t>
+          <t>722716</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>425723</t>
+          <t>672791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>731284</t>
+          <t>774915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>499606</t>
+          <t>575468</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>368131</t>
+          <t>533263</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>577074</t>
+          <t>615946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1135922</t>
+          <t>1298184</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>912437</t>
+          <t>1229067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1273737</t>
+          <t>1364384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1651225</t>
+          <t>1504831</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1556257</t>
+          <t>1452632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1861818</t>
+          <t>1554756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1733945</t>
+          <t>1590934</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1656477</t>
+          <t>1550456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1865420</t>
+          <t>1633139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3385170</t>
+          <t>3095765</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3247355</t>
+          <t>3029565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3608655</t>
+          <t>3164882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2287541</t>
+          <t>2227547</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2287541</t>
+          <t>2227547</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2287541</t>
+          <t>2227547</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2233551</t>
+          <t>2166402</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2233551</t>
+          <t>2166402</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2233551</t>
+          <t>2166402</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4521092</t>
+          <t>4393949</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4521092</t>
+          <t>4393949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4521092</t>
+          <t>4393949</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,67 +1411,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>127786</t>
+          <t>133536</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106761</t>
+          <t>111871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157867</t>
+          <t>156715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>15,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>121022</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>103827</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>142821</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>16,51%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>105003</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>88049</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>121821</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>232788</t>
+          <t>254558</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203100</t>
+          <t>226235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>267145</t>
+          <t>284710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -1524,67 +1524,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518837</t>
+          <t>578051</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>488756</t>
+          <t>554872</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539862</t>
+          <t>599716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>84,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>611963</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>590164</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>629158</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>83,49%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>554253</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>537435</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>571207</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1073091</t>
+          <t>1190014</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1038734</t>
+          <t>1159862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1102779</t>
+          <t>1218337</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659256</t>
+          <t>732985</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659256</t>
+          <t>732985</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659256</t>
+          <t>732985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305879</t>
+          <t>1444572</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305879</t>
+          <t>1444572</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305879</t>
+          <t>1444572</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>901646</t>
+          <t>1004297</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>682918</t>
+          <t>948617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>990645</t>
+          <t>1068603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>769409</t>
+          <t>882891</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>635958</t>
+          <t>837313</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>841275</t>
+          <t>934179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1671056</t>
+          <t>1887188</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1429680</t>
+          <t>1810199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1803121</t>
+          <t>1966223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2545401</t>
+          <t>2511231</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2456402</t>
+          <t>2446925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2764129</t>
+          <t>2566911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2878906</t>
+          <t>2838534</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2807040</t>
+          <t>2787246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3012357</t>
+          <t>2884112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5424306</t>
+          <t>5349765</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5292241</t>
+          <t>5270730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5665682</t>
+          <t>5426754</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3447047</t>
+          <t>3515528</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3447047</t>
+          <t>3515528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3447047</t>
+          <t>3515528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648315</t>
+          <t>3721425</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648315</t>
+          <t>3721425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648315</t>
+          <t>3721425</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7095362</t>
+          <t>7236953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7095362</t>
+          <t>7236953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7095362</t>
+          <t>7236953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
